--- a/ig/DM-JUILLET-2026/ValueSet-jdv-support-nutritionnel-cisis.xlsx
+++ b/ig/DM-JUILLET-2026/ValueSet-jdv-support-nutritionnel-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260619134043</t>
+    <t>20260716085852</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:40:43+01:00</t>
+    <t>2026-07-16T08:58:52+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
